--- a/artfynd/A 22404-2026 artfynd.xlsx
+++ b/artfynd/A 22404-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743016</v>
+        <v>122743015</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445828</v>
+        <v>445915</v>
       </c>
       <c r="R2" t="n">
-        <v>6904187</v>
+        <v>6904338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,14 +776,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743015</v>
+        <v>122743017</v>
       </c>
       <c r="B3" t="n">
-        <v>93205</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445915</v>
+        <v>445864</v>
       </c>
       <c r="R3" t="n">
-        <v>6904338</v>
+        <v>6904125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122743016</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hemtjärnen V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>445828</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6904187</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122743018</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Utkommentj. Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>445870</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6904054</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 22404-2026 artfynd.xlsx
+++ b/artfynd/A 22404-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743015</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743016</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743018</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>